--- a/utils/data-room-simulator/output/mrr_analysis.xlsx
+++ b/utils/data-room-simulator/output/mrr_analysis.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Data" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,46 +413,46 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H62"/>
+  <dimension ref="A1:H63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>period</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>active_customers</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>total_mrr</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>arr</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>average_mrr</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>new_mrr</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>churned_mrr</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>expansion_mrr</t>
         </is>
@@ -480,22 +468,22 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>2860198.25</v>
+        <v>1624383.84</v>
       </c>
       <c r="D2" t="n">
-        <v>34322379</v>
+        <v>19492606.08</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>127167.65</v>
+        <v>91805.55</v>
       </c>
       <c r="G2" t="n">
-        <v>53718.72</v>
+        <v>42636.43</v>
       </c>
       <c r="H2" t="n">
-        <v>65201.65</v>
+        <v>42369.26</v>
       </c>
     </row>
     <row r="3">
@@ -505,25 +493,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="C3" t="n">
-        <v>3084347.8</v>
+        <v>1619436.88</v>
       </c>
       <c r="D3" t="n">
-        <v>37012173.6</v>
+        <v>19433242.56</v>
       </c>
       <c r="E3" t="n">
-        <v>771086.95</v>
+        <v>73610.77</v>
       </c>
       <c r="F3" t="n">
-        <v>232350</v>
+        <v>56665.26</v>
       </c>
       <c r="G3" t="n">
-        <v>92662.82000000001</v>
+        <v>28221.35</v>
       </c>
       <c r="H3" t="n">
-        <v>40293.12</v>
+        <v>18488.65</v>
       </c>
     </row>
     <row r="4">
@@ -533,25 +521,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7</v>
+        <v>45</v>
       </c>
       <c r="C4" t="n">
-        <v>2900448.21</v>
+        <v>1767872.67</v>
       </c>
       <c r="D4" t="n">
-        <v>34805378.52</v>
+        <v>21214472.04</v>
       </c>
       <c r="E4" t="n">
-        <v>414349.74</v>
+        <v>39286.06</v>
       </c>
       <c r="F4" t="n">
-        <v>157188.56</v>
+        <v>66115.85000000001</v>
       </c>
       <c r="G4" t="n">
-        <v>39721.6</v>
+        <v>29959.16</v>
       </c>
       <c r="H4" t="n">
-        <v>70778.73</v>
+        <v>43629.53</v>
       </c>
     </row>
     <row r="5">
@@ -561,25 +549,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8</v>
+        <v>67</v>
       </c>
       <c r="C5" t="n">
-        <v>3286681.67</v>
+        <v>1917468.75</v>
       </c>
       <c r="D5" t="n">
-        <v>39440180.04</v>
+        <v>23009625</v>
       </c>
       <c r="E5" t="n">
-        <v>410835.21</v>
+        <v>28618.94</v>
       </c>
       <c r="F5" t="n">
-        <v>141590.96</v>
+        <v>119593.04</v>
       </c>
       <c r="G5" t="n">
-        <v>89230.81</v>
+        <v>64176.51</v>
       </c>
       <c r="H5" t="n">
-        <v>75229.42</v>
+        <v>35221.82</v>
       </c>
     </row>
     <row r="6">
@@ -589,25 +577,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>11</v>
+        <v>96</v>
       </c>
       <c r="C6" t="n">
-        <v>3349024.36</v>
+        <v>1921753.26</v>
       </c>
       <c r="D6" t="n">
-        <v>40188292.32</v>
+        <v>23061039.12</v>
       </c>
       <c r="E6" t="n">
-        <v>304456.76</v>
+        <v>20018.26</v>
       </c>
       <c r="F6" t="n">
-        <v>200288.05</v>
+        <v>61635.71</v>
       </c>
       <c r="G6" t="n">
-        <v>81136.58</v>
+        <v>20696.21</v>
       </c>
       <c r="H6" t="n">
-        <v>97682.14</v>
+        <v>56582.76</v>
       </c>
     </row>
     <row r="7">
@@ -617,25 +605,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>12</v>
+        <v>117</v>
       </c>
       <c r="C7" t="n">
-        <v>3528825.15</v>
+        <v>1941147.44</v>
       </c>
       <c r="D7" t="n">
-        <v>42345901.8</v>
+        <v>23293769.28</v>
       </c>
       <c r="E7" t="n">
-        <v>294068.76</v>
+        <v>16591</v>
       </c>
       <c r="F7" t="n">
-        <v>210029.62</v>
+        <v>90439.17</v>
       </c>
       <c r="G7" t="n">
-        <v>46815.51</v>
+        <v>44275.97</v>
       </c>
       <c r="H7" t="n">
-        <v>60113.88</v>
+        <v>37440.15</v>
       </c>
     </row>
     <row r="8">
@@ -645,25 +633,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>18</v>
+        <v>137</v>
       </c>
       <c r="C8" t="n">
-        <v>3786901.21</v>
+        <v>2166359.52</v>
       </c>
       <c r="D8" t="n">
-        <v>45442814.52</v>
+        <v>25996314.24</v>
       </c>
       <c r="E8" t="n">
-        <v>210383.4</v>
+        <v>15812.84</v>
       </c>
       <c r="F8" t="n">
-        <v>264872.93</v>
+        <v>169944.84</v>
       </c>
       <c r="G8" t="n">
-        <v>70466.11</v>
+        <v>50811.68</v>
       </c>
       <c r="H8" t="n">
-        <v>67140.94</v>
+        <v>42097.76</v>
       </c>
     </row>
     <row r="9">
@@ -673,25 +661,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>21</v>
+        <v>160</v>
       </c>
       <c r="C9" t="n">
-        <v>3718021.3</v>
+        <v>2058154.58</v>
       </c>
       <c r="D9" t="n">
-        <v>44616255.6</v>
+        <v>24697854.96</v>
       </c>
       <c r="E9" t="n">
-        <v>177048.63</v>
+        <v>12863.47</v>
       </c>
       <c r="F9" t="n">
-        <v>199257.24</v>
+        <v>120143.65</v>
       </c>
       <c r="G9" t="n">
-        <v>50046.54</v>
+        <v>77179.91</v>
       </c>
       <c r="H9" t="n">
-        <v>80857.99000000001</v>
+        <v>20642.97</v>
       </c>
     </row>
     <row r="10">
@@ -701,25 +689,25 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>24</v>
+        <v>182</v>
       </c>
       <c r="C10" t="n">
-        <v>3961792.51</v>
+        <v>2237675.13</v>
       </c>
       <c r="D10" t="n">
-        <v>47541510.12</v>
+        <v>26852101.56</v>
       </c>
       <c r="E10" t="n">
-        <v>165074.69</v>
+        <v>12294.92</v>
       </c>
       <c r="F10" t="n">
-        <v>288504.26</v>
+        <v>119648.14</v>
       </c>
       <c r="G10" t="n">
-        <v>119436.38</v>
+        <v>78671.03999999999</v>
       </c>
       <c r="H10" t="n">
-        <v>93656.95</v>
+        <v>48931.56</v>
       </c>
     </row>
     <row r="11">
@@ -729,25 +717,25 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>27</v>
+        <v>203</v>
       </c>
       <c r="C11" t="n">
-        <v>4611436.18</v>
+        <v>2460732.46</v>
       </c>
       <c r="D11" t="n">
-        <v>55337234.16</v>
+        <v>29528789.52</v>
       </c>
       <c r="E11" t="n">
-        <v>170793.93</v>
+        <v>12121.83</v>
       </c>
       <c r="F11" t="n">
-        <v>325747.25</v>
+        <v>192505.51</v>
       </c>
       <c r="G11" t="n">
-        <v>170426.49</v>
+        <v>40807.37</v>
       </c>
       <c r="H11" t="n">
-        <v>112867.1</v>
+        <v>33096.11</v>
       </c>
     </row>
     <row r="12">
@@ -757,25 +745,25 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>29</v>
+        <v>241</v>
       </c>
       <c r="C12" t="n">
-        <v>4362753.18</v>
+        <v>2597234.81</v>
       </c>
       <c r="D12" t="n">
-        <v>52353038.16</v>
+        <v>31166817.72</v>
       </c>
       <c r="E12" t="n">
-        <v>150439.76</v>
+        <v>10776.91</v>
       </c>
       <c r="F12" t="n">
-        <v>177746.51</v>
+        <v>160859.26</v>
       </c>
       <c r="G12" t="n">
-        <v>105398.49</v>
+        <v>77605.19</v>
       </c>
       <c r="H12" t="n">
-        <v>62343.14</v>
+        <v>33057.93</v>
       </c>
     </row>
     <row r="13">
@@ -785,25 +773,25 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>31</v>
+        <v>270</v>
       </c>
       <c r="C13" t="n">
-        <v>4195798.22</v>
+        <v>2672387.95</v>
       </c>
       <c r="D13" t="n">
-        <v>50349578.64</v>
+        <v>32068655.4</v>
       </c>
       <c r="E13" t="n">
-        <v>135348.33</v>
+        <v>9897.73</v>
       </c>
       <c r="F13" t="n">
-        <v>278824.23</v>
+        <v>152284.75</v>
       </c>
       <c r="G13" t="n">
-        <v>56884.42</v>
+        <v>71041.09</v>
       </c>
       <c r="H13" t="n">
-        <v>98998.7</v>
+        <v>37347.13</v>
       </c>
     </row>
     <row r="14">
@@ -813,25 +801,25 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>36</v>
+        <v>303</v>
       </c>
       <c r="C14" t="n">
-        <v>3350930.82</v>
+        <v>2054213.68</v>
       </c>
       <c r="D14" t="n">
-        <v>40211169.84</v>
+        <v>24650564.16</v>
       </c>
       <c r="E14" t="n">
-        <v>93081.41</v>
+        <v>6779.58</v>
       </c>
       <c r="F14" t="n">
-        <v>238915.63</v>
+        <v>129871.05</v>
       </c>
       <c r="G14" t="n">
-        <v>123614.98</v>
+        <v>64819.16</v>
       </c>
       <c r="H14" t="n">
-        <v>34203.31</v>
+        <v>45969.83</v>
       </c>
     </row>
     <row r="15">
@@ -841,25 +829,25 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>39</v>
+        <v>328</v>
       </c>
       <c r="C15" t="n">
-        <v>3460991.87</v>
+        <v>2203406.64</v>
       </c>
       <c r="D15" t="n">
-        <v>41531902.44</v>
+        <v>26440879.68</v>
       </c>
       <c r="E15" t="n">
-        <v>88743.38</v>
+        <v>6717.7</v>
       </c>
       <c r="F15" t="n">
-        <v>127519.55</v>
+        <v>168480.62</v>
       </c>
       <c r="G15" t="n">
-        <v>96243.86</v>
+        <v>71829.63</v>
       </c>
       <c r="H15" t="n">
-        <v>86773.10000000001</v>
+        <v>27654.03</v>
       </c>
     </row>
     <row r="16">
@@ -869,25 +857,25 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>44</v>
+        <v>356</v>
       </c>
       <c r="C16" t="n">
-        <v>3330011.99</v>
+        <v>2256539.51</v>
       </c>
       <c r="D16" t="n">
-        <v>39960143.88</v>
+        <v>27078474.12</v>
       </c>
       <c r="E16" t="n">
-        <v>75682.09</v>
+        <v>6338.59</v>
       </c>
       <c r="F16" t="n">
-        <v>221954.67</v>
+        <v>75807.82000000001</v>
       </c>
       <c r="G16" t="n">
-        <v>102330.38</v>
+        <v>86721.60000000001</v>
       </c>
       <c r="H16" t="n">
-        <v>94393.35000000001</v>
+        <v>53789.35</v>
       </c>
     </row>
     <row r="17">
@@ -897,25 +885,25 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>46</v>
+        <v>373</v>
       </c>
       <c r="C17" t="n">
-        <v>3562830.83</v>
+        <v>2512183.25</v>
       </c>
       <c r="D17" t="n">
-        <v>42753969.96</v>
+        <v>30146199</v>
       </c>
       <c r="E17" t="n">
-        <v>77452.84</v>
+        <v>6735.08</v>
       </c>
       <c r="F17" t="n">
-        <v>230789.48</v>
+        <v>183328.47</v>
       </c>
       <c r="G17" t="n">
-        <v>107017.1</v>
+        <v>37962.38</v>
       </c>
       <c r="H17" t="n">
-        <v>42485.39</v>
+        <v>48115.44</v>
       </c>
     </row>
     <row r="18">
@@ -925,25 +913,25 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>48</v>
+        <v>394</v>
       </c>
       <c r="C18" t="n">
-        <v>3755125.91</v>
+        <v>2498875.86</v>
       </c>
       <c r="D18" t="n">
-        <v>45061510.92</v>
+        <v>29986510.32</v>
       </c>
       <c r="E18" t="n">
-        <v>78231.78999999999</v>
+        <v>6342.32</v>
       </c>
       <c r="F18" t="n">
-        <v>254891.87</v>
+        <v>197688.94</v>
       </c>
       <c r="G18" t="n">
-        <v>103244.19</v>
+        <v>83571.42</v>
       </c>
       <c r="H18" t="n">
-        <v>38129.73</v>
+        <v>64525.99</v>
       </c>
     </row>
     <row r="19">
@@ -953,25 +941,25 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>51</v>
+        <v>417</v>
       </c>
       <c r="C19" t="n">
-        <v>3511223.88</v>
+        <v>2531887.88</v>
       </c>
       <c r="D19" t="n">
-        <v>42134686.56</v>
+        <v>30382654.56</v>
       </c>
       <c r="E19" t="n">
-        <v>68847.53</v>
+        <v>6071.67</v>
       </c>
       <c r="F19" t="n">
-        <v>151309.78</v>
+        <v>81514.45</v>
       </c>
       <c r="G19" t="n">
-        <v>55564.75</v>
+        <v>69528.99000000001</v>
       </c>
       <c r="H19" t="n">
-        <v>104807.53</v>
+        <v>60796.41</v>
       </c>
     </row>
     <row r="20">
@@ -981,25 +969,25 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>57</v>
+        <v>448</v>
       </c>
       <c r="C20" t="n">
-        <v>3669281.15</v>
+        <v>2687680.51</v>
       </c>
       <c r="D20" t="n">
-        <v>44031373.8</v>
+        <v>32252166.12</v>
       </c>
       <c r="E20" t="n">
-        <v>64373.35</v>
+        <v>5999.29</v>
       </c>
       <c r="F20" t="n">
-        <v>174697.36</v>
+        <v>98398.02</v>
       </c>
       <c r="G20" t="n">
-        <v>141589.69</v>
+        <v>97282.39</v>
       </c>
       <c r="H20" t="n">
-        <v>60484.13</v>
+        <v>53299.53</v>
       </c>
     </row>
     <row r="21">
@@ -1009,25 +997,25 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>62</v>
+        <v>473</v>
       </c>
       <c r="C21" t="n">
-        <v>3821776.1</v>
+        <v>2574485.7</v>
       </c>
       <c r="D21" t="n">
-        <v>45861313.2</v>
+        <v>30893828.4</v>
       </c>
       <c r="E21" t="n">
-        <v>61641.55</v>
+        <v>5442.89</v>
       </c>
       <c r="F21" t="n">
-        <v>165213.18</v>
+        <v>79658.35000000001</v>
       </c>
       <c r="G21" t="n">
-        <v>105295.95</v>
+        <v>43864.6</v>
       </c>
       <c r="H21" t="n">
-        <v>96169.06</v>
+        <v>44238.42</v>
       </c>
     </row>
     <row r="22">
@@ -1037,25 +1025,25 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>66</v>
+        <v>482</v>
       </c>
       <c r="C22" t="n">
-        <v>3901253.49</v>
+        <v>2731711.5</v>
       </c>
       <c r="D22" t="n">
-        <v>46815041.88</v>
+        <v>32780538</v>
       </c>
       <c r="E22" t="n">
-        <v>59109.9</v>
+        <v>5667.45</v>
       </c>
       <c r="F22" t="n">
-        <v>206510.12</v>
+        <v>106455.01</v>
       </c>
       <c r="G22" t="n">
-        <v>88011.27</v>
+        <v>90657.36</v>
       </c>
       <c r="H22" t="n">
-        <v>116289</v>
+        <v>60549.4</v>
       </c>
     </row>
     <row r="23">
@@ -1065,25 +1053,25 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>69</v>
+        <v>500</v>
       </c>
       <c r="C23" t="n">
-        <v>4523412.78</v>
+        <v>3478354.28</v>
       </c>
       <c r="D23" t="n">
-        <v>54280953.36</v>
+        <v>41740251.36</v>
       </c>
       <c r="E23" t="n">
-        <v>65556.71000000001</v>
+        <v>6956.71</v>
       </c>
       <c r="F23" t="n">
-        <v>153063.65</v>
+        <v>270114.01</v>
       </c>
       <c r="G23" t="n">
-        <v>130426.47</v>
+        <v>70321.12</v>
       </c>
       <c r="H23" t="n">
-        <v>78247.73</v>
+        <v>81552.85000000001</v>
       </c>
     </row>
     <row r="24">
@@ -1093,25 +1081,25 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>72</v>
+        <v>514</v>
       </c>
       <c r="C24" t="n">
-        <v>4470559.18</v>
+        <v>3307881.84</v>
       </c>
       <c r="D24" t="n">
-        <v>53646710.16</v>
+        <v>39694582.08</v>
       </c>
       <c r="E24" t="n">
-        <v>62091.1</v>
+        <v>6435.57</v>
       </c>
       <c r="F24" t="n">
-        <v>333993.35</v>
+        <v>218904.55</v>
       </c>
       <c r="G24" t="n">
-        <v>142904.39</v>
+        <v>99279.45</v>
       </c>
       <c r="H24" t="n">
-        <v>100762.32</v>
+        <v>94073.75</v>
       </c>
     </row>
     <row r="25">
@@ -1121,25 +1109,25 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>76</v>
+        <v>535</v>
       </c>
       <c r="C25" t="n">
-        <v>4348340.93</v>
+        <v>3503102.05</v>
       </c>
       <c r="D25" t="n">
-        <v>52180091.16</v>
+        <v>42037224.6</v>
       </c>
       <c r="E25" t="n">
-        <v>57215.01</v>
+        <v>6547.85</v>
       </c>
       <c r="F25" t="n">
-        <v>185146.09</v>
+        <v>233884.17</v>
       </c>
       <c r="G25" t="n">
-        <v>128545.34</v>
+        <v>138553.94</v>
       </c>
       <c r="H25" t="n">
-        <v>94813</v>
+        <v>91335.35000000001</v>
       </c>
     </row>
     <row r="26">
@@ -1149,25 +1137,25 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>81</v>
+        <v>559</v>
       </c>
       <c r="C26" t="n">
-        <v>3252941.51</v>
+        <v>2691437.45</v>
       </c>
       <c r="D26" t="n">
-        <v>39035298.12</v>
+        <v>32297249.4</v>
       </c>
       <c r="E26" t="n">
-        <v>40159.77</v>
+        <v>4814.74</v>
       </c>
       <c r="F26" t="n">
-        <v>181342.07</v>
+        <v>149501.2</v>
       </c>
       <c r="G26" t="n">
-        <v>96522.62</v>
+        <v>95339.98</v>
       </c>
       <c r="H26" t="n">
-        <v>85996.73</v>
+        <v>42866.34</v>
       </c>
     </row>
     <row r="27">
@@ -1177,25 +1165,25 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>84</v>
+        <v>585</v>
       </c>
       <c r="C27" t="n">
-        <v>3496405.57</v>
+        <v>2838203.14</v>
       </c>
       <c r="D27" t="n">
-        <v>41956866.84</v>
+        <v>34058437.68</v>
       </c>
       <c r="E27" t="n">
-        <v>41623.88</v>
+        <v>4851.63</v>
       </c>
       <c r="F27" t="n">
-        <v>230141.26</v>
+        <v>142170.23</v>
       </c>
       <c r="G27" t="n">
-        <v>84542.86</v>
+        <v>90865.88</v>
       </c>
       <c r="H27" t="n">
-        <v>36862.44</v>
+        <v>74572.92</v>
       </c>
     </row>
     <row r="28">
@@ -1205,25 +1193,25 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>88</v>
+        <v>595</v>
       </c>
       <c r="C28" t="n">
-        <v>3537733.42</v>
+        <v>2778400.8</v>
       </c>
       <c r="D28" t="n">
-        <v>42452801.04</v>
+        <v>33340809.6</v>
       </c>
       <c r="E28" t="n">
-        <v>40201.52</v>
+        <v>4669.58</v>
       </c>
       <c r="F28" t="n">
-        <v>117996.1</v>
+        <v>84968.81</v>
       </c>
       <c r="G28" t="n">
-        <v>82647.19</v>
+        <v>78367.45</v>
       </c>
       <c r="H28" t="n">
-        <v>69336.47</v>
+        <v>71860.64</v>
       </c>
     </row>
     <row r="29">
@@ -1233,25 +1221,25 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>94</v>
+        <v>613</v>
       </c>
       <c r="C29" t="n">
-        <v>3883829.44</v>
+        <v>3037586.22</v>
       </c>
       <c r="D29" t="n">
-        <v>46605953.28</v>
+        <v>36451034.64</v>
       </c>
       <c r="E29" t="n">
-        <v>41317.33</v>
+        <v>4955.28</v>
       </c>
       <c r="F29" t="n">
-        <v>135998.75</v>
+        <v>165469.15</v>
       </c>
       <c r="G29" t="n">
-        <v>128768.55</v>
+        <v>119956.3</v>
       </c>
       <c r="H29" t="n">
-        <v>87691.11</v>
+        <v>37845.55</v>
       </c>
     </row>
     <row r="30">
@@ -1261,25 +1249,25 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>99</v>
+        <v>635</v>
       </c>
       <c r="C30" t="n">
-        <v>3992722.57</v>
+        <v>3007141.77</v>
       </c>
       <c r="D30" t="n">
-        <v>47912670.84</v>
+        <v>36085701.24</v>
       </c>
       <c r="E30" t="n">
-        <v>40330.53</v>
+        <v>4735.66</v>
       </c>
       <c r="F30" t="n">
-        <v>180542.69</v>
+        <v>172294.71</v>
       </c>
       <c r="G30" t="n">
-        <v>158616.71</v>
+        <v>107318.43</v>
       </c>
       <c r="H30" t="n">
-        <v>47643.43</v>
+        <v>74997.11</v>
       </c>
     </row>
     <row r="31">
@@ -1289,25 +1277,25 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>105</v>
+        <v>659</v>
       </c>
       <c r="C31" t="n">
-        <v>3728537.48</v>
+        <v>2901444.3</v>
       </c>
       <c r="D31" t="n">
-        <v>44742449.76</v>
+        <v>34817331.6</v>
       </c>
       <c r="E31" t="n">
-        <v>35509.88</v>
+        <v>4402.8</v>
       </c>
       <c r="F31" t="n">
-        <v>243394.65</v>
+        <v>106694.57</v>
       </c>
       <c r="G31" t="n">
-        <v>133233.47</v>
+        <v>97957.16</v>
       </c>
       <c r="H31" t="n">
-        <v>76321.42999999999</v>
+        <v>49287.27</v>
       </c>
     </row>
     <row r="32">
@@ -1317,25 +1305,25 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>105</v>
+        <v>680</v>
       </c>
       <c r="C32" t="n">
-        <v>3979192.01</v>
+        <v>3167766.02</v>
       </c>
       <c r="D32" t="n">
-        <v>47750304.12</v>
+        <v>38013192.24</v>
       </c>
       <c r="E32" t="n">
-        <v>37897.07</v>
+        <v>4658.48</v>
       </c>
       <c r="F32" t="n">
-        <v>206324</v>
+        <v>125985.19</v>
       </c>
       <c r="G32" t="n">
-        <v>47356.77</v>
+        <v>125580.43</v>
       </c>
       <c r="H32" t="n">
-        <v>55859.02</v>
+        <v>54397.15</v>
       </c>
     </row>
     <row r="33">
@@ -1345,25 +1333,25 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>108</v>
+        <v>699</v>
       </c>
       <c r="C33" t="n">
-        <v>4073317.23</v>
+        <v>3303264.99</v>
       </c>
       <c r="D33" t="n">
-        <v>48879806.76</v>
+        <v>39639179.88</v>
       </c>
       <c r="E33" t="n">
-        <v>37715.9</v>
+        <v>4725.7</v>
       </c>
       <c r="F33" t="n">
-        <v>267506.82</v>
+        <v>170313.25</v>
       </c>
       <c r="G33" t="n">
-        <v>144864.85</v>
+        <v>71380.57000000001</v>
       </c>
       <c r="H33" t="n">
-        <v>77346.84</v>
+        <v>93867.7</v>
       </c>
     </row>
     <row r="34">
@@ -1373,25 +1361,25 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>114</v>
+        <v>716</v>
       </c>
       <c r="C34" t="n">
-        <v>3978376.3</v>
+        <v>3300452.69</v>
       </c>
       <c r="D34" t="n">
-        <v>47740515.6</v>
+        <v>39605432.28</v>
       </c>
       <c r="E34" t="n">
-        <v>34898.04</v>
+        <v>4609.57</v>
       </c>
       <c r="F34" t="n">
-        <v>125906.51</v>
+        <v>207454.82</v>
       </c>
       <c r="G34" t="n">
-        <v>45029.83</v>
+        <v>69189.41</v>
       </c>
       <c r="H34" t="n">
-        <v>76184.25</v>
+        <v>73957.96000000001</v>
       </c>
     </row>
     <row r="35">
@@ -1401,25 +1389,25 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>117</v>
+        <v>732</v>
       </c>
       <c r="C35" t="n">
-        <v>4733320.72</v>
+        <v>3835922.82</v>
       </c>
       <c r="D35" t="n">
-        <v>56799848.64</v>
+        <v>46031073.84</v>
       </c>
       <c r="E35" t="n">
-        <v>40455.73</v>
+        <v>5240.33</v>
       </c>
       <c r="F35" t="n">
-        <v>363437.85</v>
+        <v>131734.98</v>
       </c>
       <c r="G35" t="n">
-        <v>155165.1</v>
+        <v>87021.06</v>
       </c>
       <c r="H35" t="n">
-        <v>63393.8</v>
+        <v>86629.41</v>
       </c>
     </row>
     <row r="36">
@@ -1429,25 +1417,25 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>120</v>
+        <v>755</v>
       </c>
       <c r="C36" t="n">
-        <v>4797467.58</v>
+        <v>3830801.03</v>
       </c>
       <c r="D36" t="n">
-        <v>57569610.96</v>
+        <v>45969612.36</v>
       </c>
       <c r="E36" t="n">
-        <v>39978.9</v>
+        <v>5073.91</v>
       </c>
       <c r="F36" t="n">
-        <v>252445.13</v>
+        <v>186213.44</v>
       </c>
       <c r="G36" t="n">
-        <v>178914.11</v>
+        <v>44269.15</v>
       </c>
       <c r="H36" t="n">
-        <v>131306.82</v>
+        <v>44929.17</v>
       </c>
     </row>
     <row r="37">
@@ -1457,25 +1445,25 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>124</v>
+        <v>779</v>
       </c>
       <c r="C37" t="n">
-        <v>4726087.09</v>
+        <v>4041815.76</v>
       </c>
       <c r="D37" t="n">
-        <v>56713045.08</v>
+        <v>48501789.12</v>
       </c>
       <c r="E37" t="n">
-        <v>38113.61</v>
+        <v>5188.47</v>
       </c>
       <c r="F37" t="n">
-        <v>228258.08</v>
+        <v>206434.14</v>
       </c>
       <c r="G37" t="n">
-        <v>85403.73</v>
+        <v>61302.85</v>
       </c>
       <c r="H37" t="n">
-        <v>105818.03</v>
+        <v>95464.82000000001</v>
       </c>
     </row>
     <row r="38">
@@ -1485,25 +1473,25 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>127</v>
+        <v>803</v>
       </c>
       <c r="C38" t="n">
-        <v>3396911.02</v>
+        <v>3058079.82</v>
       </c>
       <c r="D38" t="n">
-        <v>40762932.24</v>
+        <v>36696957.84</v>
       </c>
       <c r="E38" t="n">
-        <v>26747.33</v>
+        <v>3808.32</v>
       </c>
       <c r="F38" t="n">
-        <v>253110.6</v>
+        <v>201875.03</v>
       </c>
       <c r="G38" t="n">
-        <v>127756.7</v>
+        <v>110642.76</v>
       </c>
       <c r="H38" t="n">
-        <v>43697.64</v>
+        <v>74890.53</v>
       </c>
     </row>
     <row r="39">
@@ -1513,25 +1501,25 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>134</v>
+        <v>812</v>
       </c>
       <c r="C39" t="n">
-        <v>3573358.88</v>
+        <v>3045130.85</v>
       </c>
       <c r="D39" t="n">
-        <v>42880306.56</v>
+        <v>36541570.2</v>
       </c>
       <c r="E39" t="n">
-        <v>26666.86</v>
+        <v>3750.16</v>
       </c>
       <c r="F39" t="n">
-        <v>157690.87</v>
+        <v>220895.9</v>
       </c>
       <c r="G39" t="n">
-        <v>61186.94</v>
+        <v>31712.2</v>
       </c>
       <c r="H39" t="n">
-        <v>102906.63</v>
+        <v>68975.35000000001</v>
       </c>
     </row>
     <row r="40">
@@ -1541,25 +1529,25 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>138</v>
+        <v>836</v>
       </c>
       <c r="C40" t="n">
-        <v>3463950.72</v>
+        <v>2961782.83</v>
       </c>
       <c r="D40" t="n">
-        <v>41567408.64</v>
+        <v>35541393.96</v>
       </c>
       <c r="E40" t="n">
-        <v>25101.09</v>
+        <v>3542.8</v>
       </c>
       <c r="F40" t="n">
-        <v>146073.02</v>
+        <v>209971.19</v>
       </c>
       <c r="G40" t="n">
-        <v>58885.34</v>
+        <v>41114.25</v>
       </c>
       <c r="H40" t="n">
-        <v>94763.52</v>
+        <v>40606.34</v>
       </c>
     </row>
     <row r="41">
@@ -1569,25 +1557,25 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>141</v>
+        <v>871</v>
       </c>
       <c r="C41" t="n">
-        <v>3870604.45</v>
+        <v>3282932.7</v>
       </c>
       <c r="D41" t="n">
-        <v>46447253.4</v>
+        <v>39395192.4</v>
       </c>
       <c r="E41" t="n">
-        <v>27451.1</v>
+        <v>3769.15</v>
       </c>
       <c r="F41" t="n">
-        <v>226156.86</v>
+        <v>133996.88</v>
       </c>
       <c r="G41" t="n">
-        <v>116175.12</v>
+        <v>100042.51</v>
       </c>
       <c r="H41" t="n">
-        <v>45261.48</v>
+        <v>52738.46</v>
       </c>
     </row>
     <row r="42">
@@ -1597,25 +1585,25 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>142</v>
+        <v>891</v>
       </c>
       <c r="C42" t="n">
-        <v>3607802.23</v>
+        <v>3493028.51</v>
       </c>
       <c r="D42" t="n">
-        <v>43293626.76</v>
+        <v>41916342.12</v>
       </c>
       <c r="E42" t="n">
-        <v>25407.06</v>
+        <v>3920.35</v>
       </c>
       <c r="F42" t="n">
-        <v>149988.66</v>
+        <v>233957.12</v>
       </c>
       <c r="G42" t="n">
-        <v>45484.85</v>
+        <v>132873.69</v>
       </c>
       <c r="H42" t="n">
-        <v>40801.95</v>
+        <v>61880.86</v>
       </c>
     </row>
     <row r="43">
@@ -1625,25 +1613,25 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>141</v>
+        <v>916</v>
       </c>
       <c r="C43" t="n">
-        <v>3947629.6</v>
+        <v>3681895.49</v>
       </c>
       <c r="D43" t="n">
-        <v>47371555.2</v>
+        <v>44182745.88</v>
       </c>
       <c r="E43" t="n">
-        <v>27997.37</v>
+        <v>4019.54</v>
       </c>
       <c r="F43" t="n">
-        <v>141418.27</v>
+        <v>227854.86</v>
       </c>
       <c r="G43" t="n">
-        <v>129127.07</v>
+        <v>68276.53</v>
       </c>
       <c r="H43" t="n">
-        <v>116020.6</v>
+        <v>63785.96</v>
       </c>
     </row>
     <row r="44">
@@ -1653,25 +1641,25 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>144</v>
+        <v>938</v>
       </c>
       <c r="C44" t="n">
-        <v>4045580.32</v>
+        <v>3760317.69</v>
       </c>
       <c r="D44" t="n">
-        <v>48546963.84</v>
+        <v>45123812.28</v>
       </c>
       <c r="E44" t="n">
-        <v>28094.31</v>
+        <v>4008.87</v>
       </c>
       <c r="F44" t="n">
-        <v>255973.47</v>
+        <v>260376.54</v>
       </c>
       <c r="G44" t="n">
-        <v>105265.88</v>
+        <v>66210.31</v>
       </c>
       <c r="H44" t="n">
-        <v>103842.91</v>
+        <v>112468.67</v>
       </c>
     </row>
     <row r="45">
@@ -1681,25 +1669,25 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>147</v>
+        <v>959</v>
       </c>
       <c r="C45" t="n">
-        <v>4148559.58</v>
+        <v>3760868.22</v>
       </c>
       <c r="D45" t="n">
-        <v>49782714.96</v>
+        <v>45130418.64</v>
       </c>
       <c r="E45" t="n">
-        <v>28221.49</v>
+        <v>3921.66</v>
       </c>
       <c r="F45" t="n">
-        <v>168863.08</v>
+        <v>212103.6</v>
       </c>
       <c r="G45" t="n">
-        <v>138423.23</v>
+        <v>131038.07</v>
       </c>
       <c r="H45" t="n">
-        <v>54994.34</v>
+        <v>62372.28</v>
       </c>
     </row>
     <row r="46">
@@ -1709,25 +1697,25 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>150</v>
+        <v>979</v>
       </c>
       <c r="C46" t="n">
-        <v>4312933.81</v>
+        <v>3828428.15</v>
       </c>
       <c r="D46" t="n">
-        <v>51755205.72</v>
+        <v>45941137.8</v>
       </c>
       <c r="E46" t="n">
-        <v>28752.89</v>
+        <v>3910.55</v>
       </c>
       <c r="F46" t="n">
-        <v>282833.1</v>
+        <v>204559.63</v>
       </c>
       <c r="G46" t="n">
-        <v>159005.55</v>
+        <v>67389.85000000001</v>
       </c>
       <c r="H46" t="n">
-        <v>61174.96</v>
+        <v>41435.91</v>
       </c>
     </row>
     <row r="47">
@@ -1737,25 +1725,25 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>154</v>
+        <v>1008</v>
       </c>
       <c r="C47" t="n">
-        <v>4838999.72</v>
+        <v>4274921.25</v>
       </c>
       <c r="D47" t="n">
-        <v>58067996.64</v>
+        <v>51299055</v>
       </c>
       <c r="E47" t="n">
-        <v>31422.08</v>
+        <v>4240.99</v>
       </c>
       <c r="F47" t="n">
-        <v>340377.73</v>
+        <v>296169.54</v>
       </c>
       <c r="G47" t="n">
-        <v>75506.03</v>
+        <v>53255.81</v>
       </c>
       <c r="H47" t="n">
-        <v>116223.77</v>
+        <v>84176.12</v>
       </c>
     </row>
     <row r="48">
@@ -1765,25 +1753,25 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>156</v>
+        <v>1039</v>
       </c>
       <c r="C48" t="n">
-        <v>5176423.45</v>
+        <v>4500117.24</v>
       </c>
       <c r="D48" t="n">
-        <v>62117081.4</v>
+        <v>54001406.88</v>
       </c>
       <c r="E48" t="n">
-        <v>33182.2</v>
+        <v>4331.2</v>
       </c>
       <c r="F48" t="n">
-        <v>291494.62</v>
+        <v>185671.18</v>
       </c>
       <c r="G48" t="n">
-        <v>122668.33</v>
+        <v>169557.43</v>
       </c>
       <c r="H48" t="n">
-        <v>147507.07</v>
+        <v>62025.06</v>
       </c>
     </row>
     <row r="49">
@@ -1793,25 +1781,25 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>156</v>
+        <v>1061</v>
       </c>
       <c r="C49" t="n">
-        <v>5531301.72</v>
+        <v>4748514.04</v>
       </c>
       <c r="D49" t="n">
-        <v>66375620.64</v>
+        <v>56982168.48</v>
       </c>
       <c r="E49" t="n">
-        <v>35457.06</v>
+        <v>4475.51</v>
       </c>
       <c r="F49" t="n">
-        <v>211975.15</v>
+        <v>262754.01</v>
       </c>
       <c r="G49" t="n">
-        <v>180716.84</v>
+        <v>123556.3</v>
       </c>
       <c r="H49" t="n">
-        <v>112925.03</v>
+        <v>132110.43</v>
       </c>
     </row>
     <row r="50">
@@ -1821,25 +1809,25 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>158</v>
+        <v>1084</v>
       </c>
       <c r="C50" t="n">
-        <v>4277972.11</v>
+        <v>3796381.26</v>
       </c>
       <c r="D50" t="n">
-        <v>51335665.32</v>
+        <v>45556575.12</v>
       </c>
       <c r="E50" t="n">
-        <v>27075.77</v>
+        <v>3502.2</v>
       </c>
       <c r="F50" t="n">
-        <v>142390.96</v>
+        <v>183362.79</v>
       </c>
       <c r="G50" t="n">
-        <v>142601.55</v>
+        <v>129790.41</v>
       </c>
       <c r="H50" t="n">
-        <v>84674.92999999999</v>
+        <v>87519.19</v>
       </c>
     </row>
     <row r="51">
@@ -1849,25 +1837,25 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>162</v>
+        <v>1102</v>
       </c>
       <c r="C51" t="n">
-        <v>4290113.72</v>
+        <v>3887907.9</v>
       </c>
       <c r="D51" t="n">
-        <v>51481364.64</v>
+        <v>46654894.8</v>
       </c>
       <c r="E51" t="n">
-        <v>26482.18</v>
+        <v>3528.05</v>
       </c>
       <c r="F51" t="n">
-        <v>304964.17</v>
+        <v>156150.79</v>
       </c>
       <c r="G51" t="n">
-        <v>162008.61</v>
+        <v>109126.29</v>
       </c>
       <c r="H51" t="n">
-        <v>56055.63</v>
+        <v>90751.8</v>
       </c>
     </row>
     <row r="52">
@@ -1877,25 +1865,25 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>163</v>
+        <v>1114</v>
       </c>
       <c r="C52" t="n">
-        <v>4442664.72</v>
+        <v>3725384.34</v>
       </c>
       <c r="D52" t="n">
-        <v>53311976.64</v>
+        <v>44704612.08</v>
       </c>
       <c r="E52" t="n">
-        <v>27255.61</v>
+        <v>3344.15</v>
       </c>
       <c r="F52" t="n">
-        <v>312065.04</v>
+        <v>135986.74</v>
       </c>
       <c r="G52" t="n">
-        <v>123820.72</v>
+        <v>63152.81</v>
       </c>
       <c r="H52" t="n">
-        <v>69252.09</v>
+        <v>49483.38</v>
       </c>
     </row>
     <row r="53">
@@ -1905,25 +1893,25 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>166</v>
+        <v>1141</v>
       </c>
       <c r="C53" t="n">
-        <v>4523680.26</v>
+        <v>4126512.41</v>
       </c>
       <c r="D53" t="n">
-        <v>54284163.12</v>
+        <v>49518148.92</v>
       </c>
       <c r="E53" t="n">
-        <v>27251.09</v>
+        <v>3616.58</v>
       </c>
       <c r="F53" t="n">
-        <v>352890.28</v>
+        <v>329465.83</v>
       </c>
       <c r="G53" t="n">
-        <v>83689.46000000001</v>
+        <v>145921.81</v>
       </c>
       <c r="H53" t="n">
-        <v>48361.22</v>
+        <v>104462.6</v>
       </c>
     </row>
     <row r="54">
@@ -1933,25 +1921,25 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>169</v>
+        <v>1174</v>
       </c>
       <c r="C54" t="n">
-        <v>4843950.85</v>
+        <v>4374810.49</v>
       </c>
       <c r="D54" t="n">
-        <v>58127410.2</v>
+        <v>52497725.88</v>
       </c>
       <c r="E54" t="n">
-        <v>28662.43</v>
+        <v>3726.41</v>
       </c>
       <c r="F54" t="n">
-        <v>238254.44</v>
+        <v>167909.24</v>
       </c>
       <c r="G54" t="n">
-        <v>141016.93</v>
+        <v>121621.31</v>
       </c>
       <c r="H54" t="n">
-        <v>118121.81</v>
+        <v>65632.14</v>
       </c>
     </row>
     <row r="55">
@@ -1961,25 +1949,25 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>175</v>
+        <v>1197</v>
       </c>
       <c r="C55" t="n">
-        <v>4864702.45</v>
+        <v>4200863.93</v>
       </c>
       <c r="D55" t="n">
-        <v>58376429.4</v>
+        <v>50410367.16</v>
       </c>
       <c r="E55" t="n">
-        <v>27798.3</v>
+        <v>3509.49</v>
       </c>
       <c r="F55" t="n">
-        <v>330321.9</v>
+        <v>167776.4</v>
       </c>
       <c r="G55" t="n">
-        <v>72406.03</v>
+        <v>81825.41</v>
       </c>
       <c r="H55" t="n">
-        <v>96619.2</v>
+        <v>100600.78</v>
       </c>
     </row>
     <row r="56">
@@ -1989,25 +1977,25 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>177</v>
+        <v>1219</v>
       </c>
       <c r="C56" t="n">
-        <v>5035917.9</v>
+        <v>4331667.3</v>
       </c>
       <c r="D56" t="n">
-        <v>60431014.8</v>
+        <v>51980007.6</v>
       </c>
       <c r="E56" t="n">
-        <v>28451.51</v>
+        <v>3553.46</v>
       </c>
       <c r="F56" t="n">
-        <v>187283.24</v>
+        <v>256270.23</v>
       </c>
       <c r="G56" t="n">
-        <v>144466.3</v>
+        <v>101025.58</v>
       </c>
       <c r="H56" t="n">
-        <v>135586.04</v>
+        <v>117341.46</v>
       </c>
     </row>
     <row r="57">
@@ -2017,25 +2005,25 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>183</v>
+        <v>1245</v>
       </c>
       <c r="C57" t="n">
-        <v>4985327.85</v>
+        <v>4443504.47</v>
       </c>
       <c r="D57" t="n">
-        <v>59823934.2</v>
+        <v>53322053.64</v>
       </c>
       <c r="E57" t="n">
-        <v>27242.23</v>
+        <v>3569.08</v>
       </c>
       <c r="F57" t="n">
-        <v>213238.64</v>
+        <v>155169.2</v>
       </c>
       <c r="G57" t="n">
-        <v>186783.1</v>
+        <v>79055.24000000001</v>
       </c>
       <c r="H57" t="n">
-        <v>75391.87</v>
+        <v>74364.35000000001</v>
       </c>
     </row>
     <row r="58">
@@ -2045,25 +2033,25 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>185</v>
+        <v>1273</v>
       </c>
       <c r="C58" t="n">
-        <v>5095143.71</v>
+        <v>4553481.52</v>
       </c>
       <c r="D58" t="n">
-        <v>61141724.52</v>
+        <v>54641778.24</v>
       </c>
       <c r="E58" t="n">
-        <v>27541.32</v>
+        <v>3576.97</v>
       </c>
       <c r="F58" t="n">
-        <v>350881.57</v>
+        <v>271144.75</v>
       </c>
       <c r="G58" t="n">
-        <v>193105.81</v>
+        <v>120215.77</v>
       </c>
       <c r="H58" t="n">
-        <v>121458.71</v>
+        <v>127615.4</v>
       </c>
     </row>
     <row r="59">
@@ -2073,25 +2061,25 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>187</v>
+        <v>1300</v>
       </c>
       <c r="C59" t="n">
-        <v>5780278.96</v>
+        <v>5656946.88</v>
       </c>
       <c r="D59" t="n">
-        <v>69363347.52</v>
+        <v>67883362.56</v>
       </c>
       <c r="E59" t="n">
-        <v>30910.58</v>
+        <v>4351.5</v>
       </c>
       <c r="F59" t="n">
-        <v>329646.16</v>
+        <v>175839.37</v>
       </c>
       <c r="G59" t="n">
-        <v>62376.37</v>
+        <v>160243.15</v>
       </c>
       <c r="H59" t="n">
-        <v>70497.97</v>
+        <v>109380.73</v>
       </c>
     </row>
     <row r="60">
@@ -2101,25 +2089,25 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>191</v>
+        <v>1318</v>
       </c>
       <c r="C60" t="n">
-        <v>6175441.86</v>
+        <v>5323757.93</v>
       </c>
       <c r="D60" t="n">
-        <v>74105302.31999999</v>
+        <v>63885095.16</v>
       </c>
       <c r="E60" t="n">
-        <v>32332.16</v>
+        <v>4039.27</v>
       </c>
       <c r="F60" t="n">
-        <v>319151.84</v>
+        <v>301514.92</v>
       </c>
       <c r="G60" t="n">
-        <v>92140.31</v>
+        <v>183757.73</v>
       </c>
       <c r="H60" t="n">
-        <v>182787.07</v>
+        <v>84494.69</v>
       </c>
     </row>
     <row r="61">
@@ -2129,25 +2117,25 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>194</v>
+        <v>1334</v>
       </c>
       <c r="C61" t="n">
-        <v>6301767.22</v>
+        <v>5609035.3</v>
       </c>
       <c r="D61" t="n">
-        <v>75621206.64</v>
+        <v>67308423.59999999</v>
       </c>
       <c r="E61" t="n">
-        <v>32483.34</v>
+        <v>4204.67</v>
       </c>
       <c r="F61" t="n">
-        <v>214847.09</v>
+        <v>225822.57</v>
       </c>
       <c r="G61" t="n">
-        <v>140773.81</v>
+        <v>131070.25</v>
       </c>
       <c r="H61" t="n">
-        <v>142844.04</v>
+        <v>95343.02</v>
       </c>
     </row>
     <row r="62">
@@ -2157,25 +2145,53 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>199</v>
+        <v>1354</v>
       </c>
       <c r="C62" t="n">
-        <v>4693332.11</v>
+        <v>4261113.82</v>
       </c>
       <c r="D62" t="n">
-        <v>56319985.32</v>
+        <v>51133365.84</v>
       </c>
       <c r="E62" t="n">
-        <v>23584.58</v>
+        <v>3147.06</v>
       </c>
       <c r="F62" t="n">
-        <v>246184.21</v>
+        <v>288466.65</v>
       </c>
       <c r="G62" t="n">
-        <v>58214.09</v>
+        <v>110485.89</v>
       </c>
       <c r="H62" t="n">
-        <v>67959.98</v>
+        <v>47330.27</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>1367</v>
+      </c>
+      <c r="C63" t="n">
+        <v>4264585.31</v>
+      </c>
+      <c r="D63" t="n">
+        <v>51175023.72</v>
+      </c>
+      <c r="E63" t="n">
+        <v>3119.67</v>
+      </c>
+      <c r="F63" t="n">
+        <v>291142.74</v>
+      </c>
+      <c r="G63" t="n">
+        <v>161212.78</v>
+      </c>
+      <c r="H63" t="n">
+        <v>116760.61</v>
       </c>
     </row>
   </sheetData>
